--- a/artfynd/A 38373-2022 artfynd.xlsx
+++ b/artfynd/A 38373-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38373-2022 artfynd.xlsx
+++ b/artfynd/A 38373-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104036350</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598946.7211981306</v>
+        <v>598947</v>
       </c>
       <c r="R2" t="n">
-        <v>6396428.684272764</v>
+        <v>6396429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -797,51 +792,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104036379</v>
+        <v>104036419</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598948.7541034594</v>
+        <v>598822</v>
       </c>
       <c r="R3" t="n">
-        <v>6396280.104445609</v>
+        <v>6396332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,6 +904,246 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104036448</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 38373, Åldersbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598758</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6396314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder från tupp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104036379</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 38373, Åldersbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598949</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396280</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
